--- a/ecommerce_analysis.xlsx
+++ b/ecommerce_analysis.xlsx
@@ -8,24 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michellealessandra/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBE547CB-87B9-5643-9A9F-E64978229C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{FD91E410-198D-0A4B-861A-0B1B50F94D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10120" yWindow="740" windowWidth="19280" windowHeight="16860" activeTab="3" xr2:uid="{E588FE28-E468-C143-8E53-DC44362C3D04}"/>
+    <workbookView xWindow="10320" yWindow="740" windowWidth="23840" windowHeight="16860" activeTab="4" xr2:uid="{E588FE28-E468-C143-8E53-DC44362C3D04}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
     <sheet name="Sheet3" sheetId="5" r:id="rId2"/>
     <sheet name="Sheet4" sheetId="6" r:id="rId3"/>
     <sheet name="Dashboard" sheetId="7" r:id="rId4"/>
-    <sheet name="messy_ecommerce_sales_data (2)" sheetId="2" r:id="rId5"/>
-    <sheet name="messy_ecommerce_sales_data" sheetId="1" r:id="rId6"/>
+    <sheet name="Sheet6" sheetId="8" r:id="rId5"/>
+    <sheet name="messy_ecommerce_sales_data (2)" sheetId="2" r:id="rId6"/>
+    <sheet name="messy_ecommerce_sales_data" sheetId="1" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="4" hidden="1">'messy_ecommerce_sales_data (2)'!$A$1:$K$74</definedName>
+    <definedName name="ExternalData_1" localSheetId="5" hidden="1">'messy_ecommerce_sales_data (2)'!$A$1:$K$74</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId7"/>
+    <pivotCache cacheId="14" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="1166" uniqueCount="321">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="1184" uniqueCount="321">
   <si>
     <t>ID</t>
   </si>
@@ -8810,7 +8811,28 @@
       <fieldGroup par="11"/>
     </cacheField>
     <cacheField name="Product" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="20">
+        <s v="Blender"/>
+        <s v="Tennis Racket"/>
+        <s v="Science"/>
+        <s v="Biography"/>
+        <s v="Comics"/>
+        <s v="Shoes"/>
+        <s v="Fiction"/>
+        <s v="Basketball"/>
+        <s v="Microwave"/>
+        <s v="Vacuum"/>
+        <s v="Lamp"/>
+        <s v="Yoga Mat"/>
+        <s v="Smartwatch"/>
+        <s v="Smartphone"/>
+        <s v="T-shirt"/>
+        <s v="Football"/>
+        <s v="Jacket"/>
+        <s v="Jeans"/>
+        <s v="Headphones"/>
+        <s v="Laptop"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Category" numFmtId="0">
       <sharedItems count="6">
@@ -8880,7 +8902,7 @@
     <s v="Customer_100"/>
     <s v="ORD-41285"/>
     <x v="0"/>
-    <s v="Blender"/>
+    <x v="0"/>
     <x v="0"/>
     <n v="3"/>
     <n v="38"/>
@@ -8893,7 +8915,7 @@
     <s v="Customer_102"/>
     <s v="ORD-84355"/>
     <x v="1"/>
-    <s v="Tennis Racket"/>
+    <x v="1"/>
     <x v="1"/>
     <n v="1"/>
     <n v="389.05"/>
@@ -8906,7 +8928,7 @@
     <s v="Customer_103"/>
     <s v="ORD-57811"/>
     <x v="2"/>
-    <s v="Science"/>
+    <x v="2"/>
     <x v="2"/>
     <n v="5"/>
     <n v="233.92"/>
@@ -8919,7 +8941,7 @@
     <s v="Customer_104"/>
     <s v="ORD-93614"/>
     <x v="3"/>
-    <s v="Biography"/>
+    <x v="3"/>
     <x v="2"/>
     <n v="1"/>
     <n v="552.51"/>
@@ -8932,7 +8954,7 @@
     <s v="Customer_105"/>
     <s v="ORD-22442"/>
     <x v="4"/>
-    <s v="Tennis Racket"/>
+    <x v="1"/>
     <x v="1"/>
     <n v="3"/>
     <n v="122.06"/>
@@ -8945,7 +8967,7 @@
     <s v="Customer_107"/>
     <s v="ORD-89122"/>
     <x v="5"/>
-    <s v="Biography"/>
+    <x v="3"/>
     <x v="2"/>
     <n v="5"/>
     <n v="587.67999999999995"/>
@@ -8958,7 +8980,7 @@
     <s v="Customer_108"/>
     <s v="ORD-64400"/>
     <x v="6"/>
-    <s v="Science"/>
+    <x v="2"/>
     <x v="2"/>
     <n v="1"/>
     <n v="600.29"/>
@@ -8971,7 +8993,7 @@
     <s v="Customer_109"/>
     <s v="ORD-18512"/>
     <x v="7"/>
-    <s v="Tennis Racket"/>
+    <x v="1"/>
     <x v="1"/>
     <n v="5"/>
     <n v="168.34"/>
@@ -8984,7 +9006,7 @@
     <s v="Customer_111"/>
     <s v="ORD-72349"/>
     <x v="8"/>
-    <s v="Comics"/>
+    <x v="4"/>
     <x v="2"/>
     <n v="2"/>
     <n v="865.77"/>
@@ -8997,7 +9019,7 @@
     <s v="Customer_112"/>
     <s v="ORD-80867"/>
     <x v="9"/>
-    <s v="Shoes"/>
+    <x v="5"/>
     <x v="3"/>
     <n v="4"/>
     <n v="752.13"/>
@@ -9010,7 +9032,7 @@
     <s v="Customer_113"/>
     <s v="ORD-23994"/>
     <x v="10"/>
-    <s v="Fiction"/>
+    <x v="6"/>
     <x v="2"/>
     <n v="1"/>
     <n v="411.81"/>
@@ -9023,7 +9045,7 @@
     <s v="Customer_115"/>
     <s v="ORD-72778"/>
     <x v="11"/>
-    <s v="Fiction"/>
+    <x v="6"/>
     <x v="2"/>
     <n v="2"/>
     <n v="796.84"/>
@@ -9036,7 +9058,7 @@
     <s v="Customer_118"/>
     <s v="ORD-96061"/>
     <x v="12"/>
-    <s v="Science"/>
+    <x v="2"/>
     <x v="2"/>
     <n v="5"/>
     <n v="247.82"/>
@@ -9049,7 +9071,7 @@
     <s v="Customer_119"/>
     <s v="ORD-76016"/>
     <x v="13"/>
-    <s v="Basketball"/>
+    <x v="7"/>
     <x v="1"/>
     <n v="4"/>
     <n v="438.19"/>
@@ -9062,7 +9084,7 @@
     <s v="Customer_121"/>
     <s v="ORD-80067"/>
     <x v="14"/>
-    <s v="Basketball"/>
+    <x v="7"/>
     <x v="1"/>
     <n v="4"/>
     <n v="523.01"/>
@@ -9075,7 +9097,7 @@
     <s v="Customer_122"/>
     <s v="ORD-21443"/>
     <x v="15"/>
-    <s v="Microwave"/>
+    <x v="8"/>
     <x v="0"/>
     <n v="2"/>
     <n v="556.92999999999995"/>
@@ -9088,7 +9110,7 @@
     <s v="Customer_123"/>
     <s v="ORD-11314"/>
     <x v="16"/>
-    <s v="Vacuum"/>
+    <x v="9"/>
     <x v="4"/>
     <n v="3"/>
     <n v="615.91"/>
@@ -9101,7 +9123,7 @@
     <s v="Customer_125"/>
     <s v="ORD-23202"/>
     <x v="17"/>
-    <s v="Comics"/>
+    <x v="4"/>
     <x v="2"/>
     <n v="4"/>
     <n v="765.69"/>
@@ -9114,7 +9136,7 @@
     <s v="Customer_126"/>
     <s v="ORD-11261"/>
     <x v="18"/>
-    <s v="Shoes"/>
+    <x v="5"/>
     <x v="3"/>
     <n v="4"/>
     <n v="836.8"/>
@@ -9127,7 +9149,7 @@
     <s v="Customer_127"/>
     <s v="ORD-65482"/>
     <x v="19"/>
-    <s v="Blender"/>
+    <x v="0"/>
     <x v="0"/>
     <n v="5"/>
     <n v="336.02"/>
@@ -9140,7 +9162,7 @@
     <s v="Customer_128"/>
     <s v="ORD-12270"/>
     <x v="20"/>
-    <s v="Lamp"/>
+    <x v="10"/>
     <x v="4"/>
     <n v="3"/>
     <n v="898.69"/>
@@ -9153,7 +9175,7 @@
     <s v="Customer_129"/>
     <s v="ORD-48863"/>
     <x v="21"/>
-    <s v="Science"/>
+    <x v="2"/>
     <x v="2"/>
     <n v="4"/>
     <n v="736.71"/>
@@ -9166,7 +9188,7 @@
     <s v="Customer_131"/>
     <s v="ORD-91396"/>
     <x v="22"/>
-    <s v="Lamp"/>
+    <x v="10"/>
     <x v="0"/>
     <n v="5"/>
     <n v="616.63"/>
@@ -9179,7 +9201,7 @@
     <s v="Customer_132"/>
     <s v="ORD-40186"/>
     <x v="23"/>
-    <s v="Yoga Mat"/>
+    <x v="11"/>
     <x v="4"/>
     <n v="1"/>
     <n v="266.7"/>
@@ -9192,7 +9214,7 @@
     <s v="Customer_135"/>
     <s v="ORD-33656"/>
     <x v="17"/>
-    <s v="Smartwatch"/>
+    <x v="12"/>
     <x v="4"/>
     <n v="4"/>
     <n v="446.19"/>
@@ -9205,7 +9227,7 @@
     <s v="Customer_138"/>
     <s v="ORD-34319"/>
     <x v="24"/>
-    <s v="Lamp"/>
+    <x v="10"/>
     <x v="0"/>
     <n v="1"/>
     <n v="531.05999999999995"/>
@@ -9218,7 +9240,7 @@
     <s v="Customer_139"/>
     <s v="ORD-38418"/>
     <x v="17"/>
-    <s v="Smartphone"/>
+    <x v="13"/>
     <x v="4"/>
     <n v="2"/>
     <n v="681.38"/>
@@ -9231,7 +9253,7 @@
     <s v="Customer_140"/>
     <s v="ORD-67096"/>
     <x v="25"/>
-    <s v="Fiction"/>
+    <x v="6"/>
     <x v="2"/>
     <n v="4"/>
     <n v="588.98"/>
@@ -9244,7 +9266,7 @@
     <s v="Customer_141"/>
     <s v="ORD-45059"/>
     <x v="26"/>
-    <s v="Fiction"/>
+    <x v="6"/>
     <x v="2"/>
     <n v="3"/>
     <n v="546.04"/>
@@ -9257,7 +9279,7 @@
     <s v="Customer_142"/>
     <s v="ORD-69018"/>
     <x v="27"/>
-    <s v="Shoes"/>
+    <x v="5"/>
     <x v="3"/>
     <n v="5"/>
     <n v="645.26"/>
@@ -9270,7 +9292,7 @@
     <s v="Customer_143"/>
     <s v="ORD-14329"/>
     <x v="28"/>
-    <s v="T-shirt"/>
+    <x v="14"/>
     <x v="3"/>
     <n v="5"/>
     <n v="826.77"/>
@@ -9283,7 +9305,7 @@
     <s v="Customer_144"/>
     <s v="ORD-89452"/>
     <x v="29"/>
-    <s v="Football"/>
+    <x v="15"/>
     <x v="1"/>
     <n v="5"/>
     <n v="849.07"/>
@@ -9296,7 +9318,7 @@
     <s v="Customer_146"/>
     <s v="ORD-32755"/>
     <x v="30"/>
-    <s v="Basketball"/>
+    <x v="7"/>
     <x v="4"/>
     <n v="2"/>
     <n v="705.42"/>
@@ -9309,7 +9331,7 @@
     <s v="Customer_147"/>
     <s v="ORD-80707"/>
     <x v="31"/>
-    <s v="Jacket"/>
+    <x v="16"/>
     <x v="3"/>
     <n v="4"/>
     <n v="596.15"/>
@@ -9322,7 +9344,7 @@
     <s v="Customer_148"/>
     <s v="ORD-38423"/>
     <x v="32"/>
-    <s v="Tennis Racket"/>
+    <x v="1"/>
     <x v="1"/>
     <n v="1"/>
     <n v="660.98"/>
@@ -9335,7 +9357,7 @@
     <s v="Customer_149"/>
     <s v="ORD-95911"/>
     <x v="33"/>
-    <s v="Comics"/>
+    <x v="4"/>
     <x v="2"/>
     <n v="5"/>
     <n v="896.38"/>
@@ -9348,7 +9370,7 @@
     <s v="Customer_150"/>
     <s v="ORD-76902"/>
     <x v="34"/>
-    <s v="Yoga Mat"/>
+    <x v="11"/>
     <x v="1"/>
     <n v="1"/>
     <n v="206.19"/>
@@ -9361,7 +9383,7 @@
     <s v="Customer_151"/>
     <s v="ORD-56552"/>
     <x v="35"/>
-    <s v="Comics"/>
+    <x v="4"/>
     <x v="2"/>
     <n v="2"/>
     <n v="457.16"/>
@@ -9374,7 +9396,7 @@
     <s v="Customer_152"/>
     <s v="ORD-72869"/>
     <x v="36"/>
-    <s v="Lamp"/>
+    <x v="10"/>
     <x v="0"/>
     <n v="3"/>
     <n v="233.11"/>
@@ -9387,7 +9409,7 @@
     <s v="Customer_153"/>
     <s v="ORD-29721"/>
     <x v="37"/>
-    <s v="Yoga Mat"/>
+    <x v="11"/>
     <x v="1"/>
     <n v="4"/>
     <n v="278.89999999999998"/>
@@ -9400,7 +9422,7 @@
     <s v="Customer_154"/>
     <s v="ORD-95990"/>
     <x v="38"/>
-    <s v="Blender"/>
+    <x v="0"/>
     <x v="0"/>
     <n v="5"/>
     <n v="789.64"/>
@@ -9413,7 +9435,7 @@
     <s v="Customer_155"/>
     <s v="ORD-20182"/>
     <x v="31"/>
-    <s v="Shoes"/>
+    <x v="5"/>
     <x v="3"/>
     <n v="1"/>
     <n v="40.950000000000003"/>
@@ -9426,7 +9448,7 @@
     <s v="Customer_157"/>
     <s v="ORD-34407"/>
     <x v="39"/>
-    <s v="Jacket"/>
+    <x v="16"/>
     <x v="3"/>
     <n v="4"/>
     <n v="275.10000000000002"/>
@@ -9439,7 +9461,7 @@
     <s v="Customer_158"/>
     <s v="ORD-35817"/>
     <x v="40"/>
-    <s v="Smartwatch"/>
+    <x v="12"/>
     <x v="4"/>
     <n v="1"/>
     <n v="933.58"/>
@@ -9452,7 +9474,7 @@
     <s v="Customer_159"/>
     <s v="ORD-98162"/>
     <x v="41"/>
-    <s v="Microwave"/>
+    <x v="8"/>
     <x v="0"/>
     <n v="3"/>
     <n v="163.16"/>
@@ -9465,7 +9487,7 @@
     <s v="Customer_160"/>
     <s v="ORD-96037"/>
     <x v="5"/>
-    <s v="Science"/>
+    <x v="2"/>
     <x v="2"/>
     <n v="5"/>
     <n v="242.52"/>
@@ -9478,7 +9500,7 @@
     <s v="Customer_161"/>
     <s v="ORD-27653"/>
     <x v="42"/>
-    <s v="Science"/>
+    <x v="2"/>
     <x v="2"/>
     <n v="4"/>
     <n v="209.32"/>
@@ -9491,7 +9513,7 @@
     <s v="Customer_162"/>
     <s v="ORD-27743"/>
     <x v="43"/>
-    <s v="Blender"/>
+    <x v="0"/>
     <x v="0"/>
     <n v="2"/>
     <n v="155.76"/>
@@ -9504,7 +9526,7 @@
     <s v="Customer_165"/>
     <s v="ORD-55695"/>
     <x v="44"/>
-    <s v="Shoes"/>
+    <x v="5"/>
     <x v="3"/>
     <n v="2"/>
     <n v="443.13"/>
@@ -9517,7 +9539,7 @@
     <s v="Customer_166"/>
     <s v="ORD-97756"/>
     <x v="45"/>
-    <s v="T-shirt"/>
+    <x v="14"/>
     <x v="4"/>
     <n v="2"/>
     <n v="569.38"/>
@@ -9530,7 +9552,7 @@
     <s v="Customer_168"/>
     <s v="ORD-53430"/>
     <x v="46"/>
-    <s v="Biography"/>
+    <x v="3"/>
     <x v="2"/>
     <n v="2"/>
     <n v="141.49"/>
@@ -9543,7 +9565,7 @@
     <s v="Customer_169"/>
     <s v="ORD-75539"/>
     <x v="47"/>
-    <s v="Basketball"/>
+    <x v="7"/>
     <x v="1"/>
     <n v="1"/>
     <n v="582.13"/>
@@ -9556,7 +9578,7 @@
     <s v="Customer_170"/>
     <s v="ORD-21530"/>
     <x v="48"/>
-    <s v="Jeans"/>
+    <x v="17"/>
     <x v="3"/>
     <n v="5"/>
     <n v="741.63"/>
@@ -9569,7 +9591,7 @@
     <s v="Customer_171"/>
     <s v="ORD-99790"/>
     <x v="49"/>
-    <s v="Shoes"/>
+    <x v="5"/>
     <x v="3"/>
     <n v="3"/>
     <n v="688.68"/>
@@ -9582,7 +9604,7 @@
     <s v="Customer_172"/>
     <s v="ORD-48008"/>
     <x v="50"/>
-    <s v="Comics"/>
+    <x v="4"/>
     <x v="2"/>
     <n v="2"/>
     <n v="942.76"/>
@@ -9595,7 +9617,7 @@
     <s v="Customer_173"/>
     <s v="ORD-42171"/>
     <x v="14"/>
-    <s v="Lamp"/>
+    <x v="10"/>
     <x v="0"/>
     <n v="5"/>
     <n v="351.89"/>
@@ -9608,7 +9630,7 @@
     <s v="Customer_174"/>
     <s v="ORD-16766"/>
     <x v="51"/>
-    <s v="Microwave"/>
+    <x v="8"/>
     <x v="4"/>
     <n v="4"/>
     <n v="187.48"/>
@@ -9621,7 +9643,7 @@
     <s v="Customer_175"/>
     <s v="ORD-56651"/>
     <x v="52"/>
-    <s v="Headphones"/>
+    <x v="18"/>
     <x v="4"/>
     <n v="1"/>
     <n v="111.36"/>
@@ -9634,7 +9656,7 @@
     <s v="Customer_176"/>
     <s v="ORD-95794"/>
     <x v="53"/>
-    <s v="Comics"/>
+    <x v="4"/>
     <x v="2"/>
     <n v="5"/>
     <n v="530.52"/>
@@ -9647,7 +9669,7 @@
     <s v="Customer_177"/>
     <s v="ORD-64136"/>
     <x v="41"/>
-    <s v="Laptop"/>
+    <x v="19"/>
     <x v="4"/>
     <n v="1"/>
     <n v="69.48"/>
@@ -9660,7 +9682,7 @@
     <s v="Customer_178"/>
     <s v="ORD-89906"/>
     <x v="54"/>
-    <s v="Tennis Racket"/>
+    <x v="1"/>
     <x v="1"/>
     <n v="3"/>
     <n v="472.14"/>
@@ -9673,7 +9695,7 @@
     <s v="Customer_179"/>
     <s v="ORD-99328"/>
     <x v="55"/>
-    <s v="Yoga Mat"/>
+    <x v="11"/>
     <x v="1"/>
     <n v="3"/>
     <n v="868.67"/>
@@ -9686,7 +9708,7 @@
     <s v="Customer_185"/>
     <s v="ORD-57123"/>
     <x v="56"/>
-    <s v="Football"/>
+    <x v="15"/>
     <x v="1"/>
     <n v="2"/>
     <n v="730.92"/>
@@ -9699,7 +9721,7 @@
     <s v="Customer_186"/>
     <s v="ORD-90569"/>
     <x v="16"/>
-    <s v="Laptop"/>
+    <x v="19"/>
     <x v="4"/>
     <n v="1"/>
     <n v="365.34"/>
@@ -9712,7 +9734,7 @@
     <s v="Customer_187"/>
     <s v="ORD-41292"/>
     <x v="57"/>
-    <s v="Smartphone"/>
+    <x v="13"/>
     <x v="4"/>
     <n v="3"/>
     <n v="882.96"/>
@@ -9725,7 +9747,7 @@
     <s v="Customer_188"/>
     <s v="ORD-58590"/>
     <x v="57"/>
-    <s v="Microwave"/>
+    <x v="8"/>
     <x v="0"/>
     <n v="5"/>
     <n v="504.05"/>
@@ -9738,7 +9760,7 @@
     <s v="Customer_189"/>
     <s v="ORD-30627"/>
     <x v="56"/>
-    <s v="Lamp"/>
+    <x v="10"/>
     <x v="0"/>
     <n v="1"/>
     <n v="814.68"/>
@@ -9751,7 +9773,7 @@
     <s v="Customer_190"/>
     <s v="ORD-38469"/>
     <x v="33"/>
-    <s v="Vacuum"/>
+    <x v="9"/>
     <x v="0"/>
     <n v="1"/>
     <n v="920.37"/>
@@ -9764,7 +9786,7 @@
     <s v="Customer_191"/>
     <s v="ORD-41810"/>
     <x v="58"/>
-    <s v="Fiction"/>
+    <x v="6"/>
     <x v="2"/>
     <n v="2"/>
     <n v="881.02"/>
@@ -9777,7 +9799,7 @@
     <s v="Customer_194"/>
     <s v="ORD-69764"/>
     <x v="59"/>
-    <s v="Lamp"/>
+    <x v="10"/>
     <x v="0"/>
     <n v="5"/>
     <n v="944.54"/>
@@ -9790,7 +9812,7 @@
     <s v="Customer_195"/>
     <s v="ORD-82876"/>
     <x v="60"/>
-    <s v="Biography"/>
+    <x v="3"/>
     <x v="2"/>
     <n v="5"/>
     <n v="817.46"/>
@@ -9803,7 +9825,7 @@
     <s v="Customer_197"/>
     <s v="ORD-79139"/>
     <x v="61"/>
-    <s v="Blender"/>
+    <x v="0"/>
     <x v="0"/>
     <n v="1"/>
     <n v="160.16"/>
@@ -9816,7 +9838,7 @@
     <s v="Customer_199"/>
     <s v="ORD-82922"/>
     <x v="62"/>
-    <s v="Blender"/>
+    <x v="0"/>
     <x v="0"/>
     <n v="5"/>
     <n v="372.28"/>
@@ -9828,7 +9850,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CE65C0D9-6EB6-104B-B8DB-BEA383CE3ADD}" name="PivotTable1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CE65C0D9-6EB6-104B-B8DB-BEA383CE3ADD}" name="PivotTable1" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -10070,7 +10092,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30755713-6A47-8847-B13B-30354CB28B77}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
+<pivotTableDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30755713-6A47-8847-B13B-30354CB28B77}" name="PivotTable2" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -10371,7 +10393,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{76E2B8EF-D627-5542-9182-0CD3B917C03A}" name="PivotTable3" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{76E2B8EF-D627-5542-9182-0CD3B917C03A}" name="PivotTable3" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -10542,6 +10564,217 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5A63F965-663F-144E-949F-68F6004AE9CA}" name="PivotTable4" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="64">
+        <item x="44"/>
+        <item x="20"/>
+        <item x="50"/>
+        <item x="57"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="34"/>
+        <item x="49"/>
+        <item x="42"/>
+        <item x="13"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="11"/>
+        <item x="62"/>
+        <item x="29"/>
+        <item x="17"/>
+        <item x="59"/>
+        <item x="26"/>
+        <item x="38"/>
+        <item x="52"/>
+        <item x="25"/>
+        <item x="9"/>
+        <item x="32"/>
+        <item x="2"/>
+        <item x="23"/>
+        <item x="40"/>
+        <item x="31"/>
+        <item x="7"/>
+        <item x="19"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="43"/>
+        <item x="12"/>
+        <item x="22"/>
+        <item x="60"/>
+        <item x="21"/>
+        <item x="61"/>
+        <item x="33"/>
+        <item x="35"/>
+        <item x="45"/>
+        <item x="30"/>
+        <item x="28"/>
+        <item x="37"/>
+        <item x="58"/>
+        <item x="53"/>
+        <item x="10"/>
+        <item x="41"/>
+        <item x="24"/>
+        <item x="47"/>
+        <item x="56"/>
+        <item x="55"/>
+        <item x="54"/>
+        <item x="51"/>
+        <item x="36"/>
+        <item x="48"/>
+        <item x="16"/>
+        <item x="14"/>
+        <item x="3"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="27"/>
+        <item x="46"/>
+        <item x="39"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="21">
+        <item x="7"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="10"/>
+        <item x="19"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="13"/>
+        <item x="12"/>
+        <item x="14"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="6">
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item x="4"/>
+        <item h="1" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0">
+      <items count="14">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="9" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Count of Order_ID" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -11195,6 +11428,148 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{721F3E61-AB81-E840-B123-F62EA3A6685D}">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B5" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B17" s="2">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1002C2B-8E45-D543-A3ED-DD12B8D6A740}">
   <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -13810,7 +14185,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4984F7-2914-F544-B7C8-1B3C1928E5E8}">
   <dimension ref="A1:K104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
